--- a/artfynd/A 45868-2024 artfynd.xlsx
+++ b/artfynd/A 45868-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150388</v>
       </c>
       <c r="B2" t="n">
-        <v>78335</v>
+        <v>78338</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150387</v>
+        <v>121150389</v>
       </c>
       <c r="B3" t="n">
-        <v>91955</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658736</v>
+        <v>658753</v>
       </c>
       <c r="R3" t="n">
-        <v>7201897</v>
+        <v>7201892</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150389</v>
+        <v>121150387</v>
       </c>
       <c r="B4" t="n">
-        <v>78334</v>
+        <v>91965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658753</v>
+        <v>658736</v>
       </c>
       <c r="R4" t="n">
-        <v>7201892</v>
+        <v>7201897</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 45868-2024 artfynd.xlsx
+++ b/artfynd/A 45868-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150388</v>
+        <v>121150387</v>
       </c>
       <c r="B2" t="n">
-        <v>78338</v>
+        <v>91965</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658753</v>
+        <v>658736</v>
       </c>
       <c r="R2" t="n">
-        <v>7201892</v>
+        <v>7201897</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150389</v>
+        <v>121150388</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>78338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150387</v>
+        <v>121150389</v>
       </c>
       <c r="B4" t="n">
-        <v>91965</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658736</v>
+        <v>658753</v>
       </c>
       <c r="R4" t="n">
-        <v>7201897</v>
+        <v>7201892</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 45868-2024 artfynd.xlsx
+++ b/artfynd/A 45868-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150387</v>
+        <v>121150388</v>
       </c>
       <c r="B2" t="n">
-        <v>91965</v>
+        <v>78341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658736</v>
+        <v>658753</v>
       </c>
       <c r="R2" t="n">
-        <v>7201897</v>
+        <v>7201892</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150388</v>
+        <v>121150387</v>
       </c>
       <c r="B3" t="n">
-        <v>78338</v>
+        <v>91977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658753</v>
+        <v>658736</v>
       </c>
       <c r="R3" t="n">
-        <v>7201892</v>
+        <v>7201897</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121150389</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45868-2024 artfynd.xlsx
+++ b/artfynd/A 45868-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150387</v>
+        <v>121150389</v>
       </c>
       <c r="B3" t="n">
-        <v>91977</v>
+        <v>78340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658736</v>
+        <v>658753</v>
       </c>
       <c r="R3" t="n">
-        <v>7201897</v>
+        <v>7201892</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150389</v>
+        <v>121150387</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>91978</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658753</v>
+        <v>658736</v>
       </c>
       <c r="R4" t="n">
-        <v>7201892</v>
+        <v>7201897</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 45868-2024 artfynd.xlsx
+++ b/artfynd/A 45868-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150388</v>
+        <v>121150387</v>
       </c>
       <c r="B2" t="n">
-        <v>78341</v>
+        <v>91981</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658753</v>
+        <v>658736</v>
       </c>
       <c r="R2" t="n">
-        <v>7201892</v>
+        <v>7201897</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150389</v>
+        <v>121150388</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150387</v>
+        <v>121150389</v>
       </c>
       <c r="B4" t="n">
-        <v>91978</v>
+        <v>78343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658736</v>
+        <v>658753</v>
       </c>
       <c r="R4" t="n">
-        <v>7201897</v>
+        <v>7201892</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 45868-2024 artfynd.xlsx
+++ b/artfynd/A 45868-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150387</v>
+        <v>121150389</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>78343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658736</v>
+        <v>658753</v>
       </c>
       <c r="R2" t="n">
-        <v>7201897</v>
+        <v>7201892</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150389</v>
+        <v>121150387</v>
       </c>
       <c r="B4" t="n">
-        <v>78343</v>
+        <v>91981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658753</v>
+        <v>658736</v>
       </c>
       <c r="R4" t="n">
-        <v>7201892</v>
+        <v>7201897</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
